--- a/data/01-12-2025-Categories.xlsx
+++ b/data/01-12-2025-Categories.xlsx
@@ -771,7 +771,7 @@
         <v>45879</v>
       </c>
       <c r="K2" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -806,7 +806,7 @@
         <v>45879</v>
       </c>
       <c r="K3" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -841,7 +841,7 @@
         <v>45879</v>
       </c>
       <c r="K4" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -876,7 +876,7 @@
         <v>45879</v>
       </c>
       <c r="K5" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -911,7 +911,7 @@
         <v>45879</v>
       </c>
       <c r="K6" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -946,7 +946,7 @@
         <v>45879</v>
       </c>
       <c r="K7" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -981,7 +981,7 @@
         <v>45879</v>
       </c>
       <c r="K8" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1016,7 +1016,7 @@
         <v>45891</v>
       </c>
       <c r="K9" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1051,7 +1051,7 @@
         <v>45890</v>
       </c>
       <c r="K10" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1086,7 +1086,7 @@
         <v>45934</v>
       </c>
       <c r="K11" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1121,7 +1121,7 @@
         <v>45879</v>
       </c>
       <c r="K12" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1156,7 +1156,7 @@
         <v>45879</v>
       </c>
       <c r="K13" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1191,7 +1191,7 @@
         <v>45890</v>
       </c>
       <c r="K14" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1226,7 +1226,7 @@
         <v>45962</v>
       </c>
       <c r="K15" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1261,7 +1261,7 @@
         <v>45962</v>
       </c>
       <c r="K16" s="3">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1296,7 +1296,7 @@
         <v>45975</v>
       </c>
       <c r="K17" s="6">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1331,7 +1331,7 @@
         <v>45984</v>
       </c>
       <c r="K18" s="9">
-        <v>45991.68118306713</v>
+        <v>45992.47356619213</v>
       </c>
     </row>
   </sheetData>
